--- a/data/trans_dic/P8_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P8_2_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,58; 16,41</t>
+          <t>11,26; 16,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,8; 18,98</t>
+          <t>13,51; 19,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 18,66</t>
+          <t>13,12; 18,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 20,18</t>
+          <t>14,27; 20,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,1; 26,24</t>
+          <t>20,35; 26,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,62; 30,45</t>
+          <t>23,59; 30,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,92; 28,74</t>
+          <t>21,99; 28,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,73; 23,77</t>
+          <t>16,61; 23,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,54; 20,72</t>
+          <t>16,55; 20,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 23,85</t>
+          <t>19,35; 23,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 22,67</t>
+          <t>18,29; 22,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 21,31</t>
+          <t>16,83; 21,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 15,3</t>
+          <t>10,95; 15,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 19,15</t>
+          <t>14,01; 18,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,68</t>
+          <t>12,16; 16,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 61,87</t>
+          <t>11,37; 65,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 25,7</t>
+          <t>20,17; 25,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,61; 28,19</t>
+          <t>22,64; 28,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,48; 27,2</t>
+          <t>21,58; 27,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 24,78</t>
+          <t>20,57; 24,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 19,87</t>
+          <t>16,23; 19,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 23,0</t>
+          <t>19,15; 22,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,44; 21,13</t>
+          <t>17,59; 21,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,15; 50,4</t>
+          <t>16,97; 51,07</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,9; 18,46</t>
+          <t>12,75; 18,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 15,47</t>
+          <t>10,03; 15,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 16,69</t>
+          <t>11,56; 16,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,15; 21,12</t>
+          <t>15,09; 20,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,94; 28,17</t>
+          <t>21,99; 28,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,94; 26,29</t>
+          <t>19,98; 26,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,79</t>
+          <t>18,58; 24,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 22,68</t>
+          <t>8,31; 22,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 22,39</t>
+          <t>18,01; 22,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,06</t>
+          <t>15,91; 19,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 20,02</t>
+          <t>15,81; 19,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,18; 20,35</t>
+          <t>11,5; 20,23</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,08</t>
+          <t>11,94; 16,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 19,23</t>
+          <t>14,14; 19,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,9</t>
+          <t>11,91; 16,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,44</t>
+          <t>13,3; 17,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,42; 25,68</t>
+          <t>19,97; 25,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,65; 30,22</t>
+          <t>24,42; 30,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,36</t>
+          <t>18,28; 23,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 25,22</t>
+          <t>18,11; 25,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 20,17</t>
+          <t>16,98; 20,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 24,28</t>
+          <t>20,4; 24,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 19,6</t>
+          <t>16,07; 19,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,54; 20,89</t>
+          <t>16,86; 20,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,84; 15,12</t>
+          <t>12,7; 15,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 16,92</t>
+          <t>14,25; 16,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 15,8</t>
+          <t>13,24; 15,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 38,42</t>
+          <t>14,81; 38,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,77; 24,82</t>
+          <t>21,82; 24,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,1; 27,25</t>
+          <t>24,27; 27,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,43; 24,37</t>
+          <t>21,44; 24,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,73</t>
+          <t>16,86; 22,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 19,68</t>
+          <t>17,73; 19,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,65</t>
+          <t>19,78; 21,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 19,71</t>
+          <t>17,73; 19,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,73; 31,44</t>
+          <t>17,66; 29,04</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a subir varios pisos</t>
+          <t>Población con limitación a subir varios pisos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80341; 113871</t>
+          <t>78117; 113792</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97079; 133529</t>
+          <t>95027; 135213</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86498; 125943</t>
+          <t>88508; 125833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90302; 128255</t>
+          <t>90684; 130054</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>138357; 180592</t>
+          <t>140087; 183177</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>164616; 212234</t>
+          <t>164431; 211926</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>147456; 193342</t>
+          <t>147954; 192076</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>121339; 172399</t>
+          <t>120485; 171721</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>228701; 286483</t>
+          <t>228784; 283929</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270779; 334056</t>
+          <t>270966; 332399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>246499; 305456</t>
+          <t>246477; 305220</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>226082; 289948</t>
+          <t>229038; 288526</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>104408; 147130</t>
+          <t>105276; 147388</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>145543; 194912</t>
+          <t>142641; 191896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124882; 170539</t>
+          <t>124313; 167602</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135320; 738009</t>
+          <t>135679; 785906</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194337; 248881</t>
+          <t>195323; 250844</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>233123; 290660</t>
+          <t>233438; 291763</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>223981; 283695</t>
+          <t>225109; 285051</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>199657; 237429</t>
+          <t>197127; 237262</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>314742; 383434</t>
+          <t>313193; 377716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>395385; 471238</t>
+          <t>392367; 467293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>360244; 436403</t>
+          <t>363338; 438053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>368855; 1084029</t>
+          <t>365068; 1098575</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>87537; 125235</t>
+          <t>86531; 124805</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77287; 117178</t>
+          <t>76021; 116053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86753; 126805</t>
+          <t>87817; 126755</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106649; 148684</t>
+          <t>106249; 146511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>150001; 192637</t>
+          <t>150353; 194116</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>154967; 204318</t>
+          <t>155278; 205364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>146207; 194591</t>
+          <t>145884; 195458</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83048; 211642</t>
+          <t>77524; 209680</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>245652; 305090</t>
+          <t>245325; 301974</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>242186; 307842</t>
+          <t>244259; 306436</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>246675; 309212</t>
+          <t>244134; 306044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>183027; 333230</t>
+          <t>188280; 331170</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>111423; 151548</t>
+          <t>112464; 153054</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>132390; 181532</t>
+          <t>133491; 180503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115491; 158424</t>
+          <t>111695; 154853</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120413; 161603</t>
+          <t>123276; 163127</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>212085; 266680</t>
+          <t>207412; 264323</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>259308; 317842</t>
+          <t>256900; 316486</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>190595; 243851</t>
+          <t>190828; 247134</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>199645; 276008</t>
+          <t>198228; 277822</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>332074; 399606</t>
+          <t>336262; 401815</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>411015; 484531</t>
+          <t>407075; 484099</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>317135; 388428</t>
+          <t>318312; 388759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>334223; 422292</t>
+          <t>340711; 420600</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>420700; 495339</t>
+          <t>416239; 495773</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>492333; 579094</t>
+          <t>487710; 575578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>451351; 536199</t>
+          <t>449509; 537346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>512669; 1328973</t>
+          <t>512202; 1322235</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>735747; 838704</t>
+          <t>737279; 836512</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>857459; 969377</t>
+          <t>863317; 968987</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>759547; 863753</t>
+          <t>760064; 861693</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>627069; 843638</t>
+          <t>625698; 843437</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1178324; 1310043</t>
+          <t>1180066; 1302736</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1378450; 1511431</t>
+          <t>1380738; 1515148</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1227561; 1367649</t>
+          <t>1230276; 1365649</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1271347; 2254535</t>
+          <t>1265988; 2082517</t>
         </is>
       </c>
     </row>
